--- a/90_管理/作業スケジュール.xlsx
+++ b/90_管理/作業スケジュール.xlsx
@@ -8,26 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BDFF94-BF82-4C99-8972-E480DCE7A302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301043D1-7820-410B-9A3B-F8AC24E6034E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7785" yWindow="30" windowWidth="20445" windowHeight="15855" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="75" windowWidth="22680" windowHeight="13305" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="17" r:id="rId1"/>
-    <sheet name="進捗管理 (2)" sheetId="18" state="hidden" r:id="rId2"/>
-    <sheet name="List" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="実装・単体スケジュール" sheetId="19" r:id="rId2"/>
+    <sheet name="進捗管理 (2)" sheetId="18" state="hidden" r:id="rId3"/>
+    <sheet name="List" sheetId="2" state="hidden" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="_1Module1_.MARU" localSheetId="0">[1]!_1Module1_.MARU</definedName>
     <definedName name="_1Module1_.MARU" localSheetId="1">[1]!_1Module1_.MARU</definedName>
+    <definedName name="_1Module1_.MARU" localSheetId="2">[1]!_1Module1_.MARU</definedName>
     <definedName name="_1Module1_.MARU">[1]!_1Module1_.MARU</definedName>
     <definedName name="_2a1_" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="_a1" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">スケジュール!$A$3:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'進捗管理 (2)'!$A$3:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">実装・単体スケジュール!$A$3:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'進捗管理 (2)'!$A$3:$M$21</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
     <definedName name="a" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="AAA" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
@@ -41,17 +44,21 @@
     <definedName name="bbbb" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="D" localSheetId="0">[1]!D</definedName>
     <definedName name="D" localSheetId="1">[1]!D</definedName>
+    <definedName name="D" localSheetId="2">[1]!D</definedName>
     <definedName name="D">[1]!D</definedName>
     <definedName name="E" localSheetId="0">[1]!E</definedName>
     <definedName name="E" localSheetId="1">[1]!E</definedName>
+    <definedName name="E" localSheetId="2">[1]!E</definedName>
     <definedName name="E">[1]!E</definedName>
     <definedName name="er" localSheetId="0">[1]!er</definedName>
     <definedName name="er" localSheetId="1">[1]!er</definedName>
+    <definedName name="er" localSheetId="2">[1]!er</definedName>
     <definedName name="er">[1]!er</definedName>
     <definedName name="f" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="ff" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="help" localSheetId="0">[1]!help</definedName>
     <definedName name="help" localSheetId="1">[1]!help</definedName>
+    <definedName name="help" localSheetId="2">[1]!help</definedName>
     <definedName name="help">[1]!help</definedName>
     <definedName name="HTML_CodePage" hidden="1">932</definedName>
     <definedName name="HTML_Control" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
@@ -73,58 +80,74 @@
     <definedName name="IBE09000チェック仕様" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="j" localSheetId="0">[1]!j</definedName>
     <definedName name="j" localSheetId="1">[1]!j</definedName>
+    <definedName name="j" localSheetId="2">[1]!j</definedName>
     <definedName name="j">[1]!j</definedName>
     <definedName name="k" localSheetId="0">[1]!k</definedName>
     <definedName name="k" localSheetId="1">[1]!k</definedName>
+    <definedName name="k" localSheetId="2">[1]!k</definedName>
     <definedName name="k">[1]!k</definedName>
     <definedName name="kurikoshi" localSheetId="0">[1]!kurikoshi</definedName>
     <definedName name="kurikoshi" localSheetId="1">[1]!kurikoshi</definedName>
+    <definedName name="kurikoshi" localSheetId="2">[1]!kurikoshi</definedName>
     <definedName name="kurikoshi">[1]!kurikoshi</definedName>
     <definedName name="l" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="ll" localSheetId="0">[1]!ll</definedName>
     <definedName name="ll" localSheetId="1">[1]!ll</definedName>
+    <definedName name="ll" localSheetId="2">[1]!ll</definedName>
     <definedName name="ll">[1]!ll</definedName>
     <definedName name="MARA" localSheetId="0">[1]!MARA</definedName>
     <definedName name="MARA" localSheetId="1">[1]!MARA</definedName>
+    <definedName name="MARA" localSheetId="2">[1]!MARA</definedName>
     <definedName name="MARA">[1]!MARA</definedName>
     <definedName name="MARU" localSheetId="0">[1]!MARU</definedName>
     <definedName name="MARU" localSheetId="1">[1]!MARU</definedName>
+    <definedName name="MARU" localSheetId="2">[1]!MARU</definedName>
     <definedName name="MARU">[1]!MARU</definedName>
     <definedName name="mi" localSheetId="0">[1]!mi</definedName>
     <definedName name="mi" localSheetId="1">[1]!mi</definedName>
+    <definedName name="mi" localSheetId="2">[1]!mi</definedName>
     <definedName name="mi">[1]!mi</definedName>
     <definedName name="mi_blue" localSheetId="0">[1]!mi_blue</definedName>
     <definedName name="mi_blue" localSheetId="1">[1]!mi_blue</definedName>
+    <definedName name="mi_blue" localSheetId="2">[1]!mi_blue</definedName>
     <definedName name="mi_blue">[1]!mi_blue</definedName>
     <definedName name="Module1.MARU" localSheetId="0">[1]!Module1.MARU</definedName>
     <definedName name="Module1.MARU" localSheetId="1">[1]!Module1.MARU</definedName>
+    <definedName name="Module1.MARU" localSheetId="2">[1]!Module1.MARU</definedName>
     <definedName name="Module1.MARU">[1]!Module1.MARU</definedName>
     <definedName name="o" hidden="1">{#N/A,#N/A,FALSE,"１）背景";#N/A,#N/A,FALSE,"２）前提事項";#N/A,#N/A,FALSE,"３）優先順位";#N/A,#N/A,FALSE,"４）改善サマリー";#N/A,#N/A,FALSE,"５）懸念-1";#N/A,#N/A,FALSE,"５）懸念-2";#N/A,#N/A,FALSE,"５）懸念-3";#N/A,#N/A,FALSE,"５）懸念-4";#N/A,#N/A,FALSE,"６）組織図";#N/A,#N/A,FALSE,"６）スケジュール"}</definedName>
     <definedName name="ooo" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">スケジュール!$A$1:$E$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'進捗管理 (2)'!$A$1:$M$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">実装・単体スケジュール!$A$1:$D$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'進捗管理 (2)'!$A$1:$M$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">スケジュール!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'進捗管理 (2)'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">実装・単体スケジュール!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'進捗管理 (2)'!$1:$3</definedName>
     <definedName name="Question1" localSheetId="0">[1]!Question1</definedName>
     <definedName name="Question1" localSheetId="1">[1]!Question1</definedName>
+    <definedName name="Question1" localSheetId="2">[1]!Question1</definedName>
     <definedName name="Question1">[1]!Question1</definedName>
     <definedName name="ｒｒ" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="S">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="SANKAKU" localSheetId="0">[1]!SANKAKU</definedName>
     <definedName name="SANKAKU" localSheetId="1">[1]!SANKAKU</definedName>
+    <definedName name="SANKAKU" localSheetId="2">[1]!SANKAKU</definedName>
     <definedName name="SANKAKU">[1]!SANKAKU</definedName>
     <definedName name="ｓｄｆｓｄｆｓｄｆｓｄｆ" hidden="1">{#N/A,#N/A,FALSE,"１）背景";#N/A,#N/A,FALSE,"２）前提事項";#N/A,#N/A,FALSE,"３）優先順位";#N/A,#N/A,FALSE,"４）改善サマリー";#N/A,#N/A,FALSE,"５）懸念-1";#N/A,#N/A,FALSE,"５）懸念-2";#N/A,#N/A,FALSE,"５）懸念-3";#N/A,#N/A,FALSE,"５）懸念-4";#N/A,#N/A,FALSE,"６）組織図";#N/A,#N/A,FALSE,"６）スケジュール"}</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">#REF!</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="solver_opt" hidden="1">#REF!</definedName>
     <definedName name="vvvv" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="vvvvvvvvvvvvvvvv" hidden="1">{#N/A,#N/A,FALSE,"１）背景";#N/A,#N/A,FALSE,"２）前提事項";#N/A,#N/A,FALSE,"３）優先順位";#N/A,#N/A,FALSE,"４）改善サマリー";#N/A,#N/A,FALSE,"５）懸念-1";#N/A,#N/A,FALSE,"５）懸念-2";#N/A,#N/A,FALSE,"５）懸念-3";#N/A,#N/A,FALSE,"５）懸念-4";#N/A,#N/A,FALSE,"６）組織図";#N/A,#N/A,FALSE,"６）スケジュール"}</definedName>
     <definedName name="w" localSheetId="0">[1]!w</definedName>
     <definedName name="w" localSheetId="1">[1]!w</definedName>
+    <definedName name="w" localSheetId="2">[1]!w</definedName>
     <definedName name="w">[1]!w</definedName>
     <definedName name="wew" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="ｗｑｗｑ" localSheetId="0">[1]!ｗｑｗｑ</definedName>
     <definedName name="ｗｑｗｑ" localSheetId="1">[1]!ｗｑｗｑ</definedName>
+    <definedName name="ｗｑｗｑ" localSheetId="2">[1]!ｗｑｗｑ</definedName>
     <definedName name="ｗｑｗｑ">[1]!ｗｑｗｑ</definedName>
     <definedName name="wrn.すべて印刷." hidden="1">{#N/A,#N/A,FALSE,"１）背景";#N/A,#N/A,FALSE,"２）前提事項";#N/A,#N/A,FALSE,"３）優先順位";#N/A,#N/A,FALSE,"４）改善サマリー";#N/A,#N/A,FALSE,"５）懸念-1";#N/A,#N/A,FALSE,"５）懸念-2";#N/A,#N/A,FALSE,"５）懸念-3";#N/A,#N/A,FALSE,"５）懸念-4";#N/A,#N/A,FALSE,"６）組織図";#N/A,#N/A,FALSE,"６）スケジュール"}</definedName>
     <definedName name="wwwww" hidden="1">{#N/A,#N/A,FALSE,"１）背景";#N/A,#N/A,FALSE,"２）前提事項";#N/A,#N/A,FALSE,"３）優先順位";#N/A,#N/A,FALSE,"４）改善サマリー";#N/A,#N/A,FALSE,"５）懸念-1";#N/A,#N/A,FALSE,"５）懸念-2";#N/A,#N/A,FALSE,"５）懸念-3";#N/A,#N/A,FALSE,"５）懸念-4";#N/A,#N/A,FALSE,"６）組織図";#N/A,#N/A,FALSE,"６）スケジュール"}</definedName>
@@ -184,7 +207,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="109">
   <si>
     <t>工程</t>
     <rPh sb="0" eb="2">
@@ -1135,6 +1158,86 @@
   </si>
   <si>
     <t>SKY</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>トップ画面</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>申請画面</t>
+    <rPh sb="0" eb="2">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>申請確認画面</t>
+    <rPh sb="0" eb="2">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>申請完了画面</t>
+    <rPh sb="0" eb="2">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>申請可能製品連携ジョブ</t>
+    <rPh sb="0" eb="4">
+      <t>シンセイカノウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>レンケイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>証明書連携ジョブ</t>
+    <rPh sb="0" eb="3">
+      <t>ショウメイショ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>レンケイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>候</t>
+    <rPh sb="0" eb="1">
+      <t>コウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>熊</t>
+    <rPh sb="0" eb="1">
+      <t>クマ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -2024,7 +2127,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2213,6 +2316,12 @@
     </xf>
     <xf numFmtId="183" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2596,6 +2705,18 @@
       <font>
         <b/>
         <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
       <fill>
@@ -2611,18 +2732,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2906,8 +3015,8 @@
       <xdr:rowOff>44823</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>2292</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>338910</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>268941</xdr:rowOff>
     </xdr:to>
@@ -2925,7 +3034,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6790763" y="537882"/>
-          <a:ext cx="1728000" cy="224118"/>
+          <a:ext cx="2412000" cy="224118"/>
         </a:xfrm>
         <a:prstGeom prst="homePlate">
           <a:avLst/>
@@ -2971,14 +3080,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>56031</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>313764</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>313765</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>279231</xdr:rowOff>
     </xdr:to>
@@ -2995,7 +3104,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11295529" y="1176619"/>
+          <a:off x="11990294" y="1176619"/>
           <a:ext cx="661147" cy="223200"/>
         </a:xfrm>
         <a:prstGeom prst="homePlate">
@@ -3042,14 +3151,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>7057</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>343233</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>56029</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>336616</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>24792</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>279229</xdr:rowOff>
     </xdr:to>
@@ -3066,8 +3175,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7828763" y="862853"/>
-          <a:ext cx="3456000" cy="223200"/>
+          <a:off x="9207086" y="862853"/>
+          <a:ext cx="2808000" cy="223200"/>
         </a:xfrm>
         <a:prstGeom prst="homePlate">
           <a:avLst/>
@@ -3383,6 +3492,492 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>56030</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>313763</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>279230</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="矢印: 五方向 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F83B67E-1427-4D26-A0B0-37160547062E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8516470" y="862854"/>
+          <a:ext cx="661146" cy="223200"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>11205</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>67235</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>324441</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>290435</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="矢印: 五方向 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52EFEAF4-6E3A-4F4D-B4B7-AC3901BBD075}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7485529" y="560294"/>
+          <a:ext cx="1008000" cy="223200"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>11203</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>324969</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>268024</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="矢印: 五方向 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39DF4077-0343-45F6-B001-445A5F8ED7E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7832909" y="1781736"/>
+          <a:ext cx="661148" cy="223200"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>11204</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>324969</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>268024</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="矢印: 五方向 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{022D8B08-EFDA-4BA6-8FE3-D3577A213859}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8527675" y="2084295"/>
+          <a:ext cx="661147" cy="223200"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>179296</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>179296</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D117A4D-26AD-400D-83C7-D5DACBCB71AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8001002" y="493059"/>
+          <a:ext cx="0" cy="1848970"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>11205</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>56031</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>324968</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>279231</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="矢印: 五方向 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA8F8511-28C3-0273-2791-E97E1BA5E81A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9222440" y="1176619"/>
+          <a:ext cx="661146" cy="223200"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>11204</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>44825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>324968</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>268025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="矢印: 五方向 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20E2F64F-1F0E-24EF-A7F0-AC67314CEC2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9917204" y="1479178"/>
+          <a:ext cx="661146" cy="223200"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4175,6 +4770,295 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B460171-6980-4D03-948B-7D5B3E8C8A63}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:T8"/>
+  <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="16" customWidth="1"/>
+    <col min="4" max="4" width="1" customWidth="1"/>
+    <col min="5" max="20" width="4.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="10.5" customHeight="1">
+      <c r="A1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="48"/>
+    </row>
+    <row r="2" spans="1:20" ht="28.5" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="52">
+        <v>1</v>
+      </c>
+      <c r="F2" s="52">
+        <v>2</v>
+      </c>
+      <c r="G2" s="52">
+        <v>3</v>
+      </c>
+      <c r="H2" s="52">
+        <v>4</v>
+      </c>
+      <c r="I2" s="52">
+        <v>1</v>
+      </c>
+      <c r="J2" s="52">
+        <v>2</v>
+      </c>
+      <c r="K2" s="52">
+        <v>3</v>
+      </c>
+      <c r="L2" s="52">
+        <v>4</v>
+      </c>
+      <c r="M2" s="52">
+        <v>1</v>
+      </c>
+      <c r="N2" s="52">
+        <v>2</v>
+      </c>
+      <c r="O2" s="52">
+        <v>3</v>
+      </c>
+      <c r="P2" s="52">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="52">
+        <v>1</v>
+      </c>
+      <c r="R2" s="52">
+        <v>2</v>
+      </c>
+      <c r="S2" s="52">
+        <v>3</v>
+      </c>
+      <c r="T2" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="24.75" customHeight="1">
+      <c r="A3" s="63">
+        <v>1</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="49"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="51"/>
+    </row>
+    <row r="4" spans="1:20" ht="24.75" customHeight="1">
+      <c r="A4" s="63">
+        <f>A3+1</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="51"/>
+    </row>
+    <row r="5" spans="1:20" ht="24.75" customHeight="1">
+      <c r="A5" s="63">
+        <f>A4+1</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="49"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="51"/>
+    </row>
+    <row r="6" spans="1:20" ht="24.2" customHeight="1">
+      <c r="A6" s="63">
+        <f>A5+1</f>
+        <v>4</v>
+      </c>
+      <c r="B6" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="49"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="50"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="51"/>
+    </row>
+    <row r="7" spans="1:20" ht="24.2" customHeight="1">
+      <c r="A7" s="52">
+        <f>A6+1</f>
+        <v>5</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="59"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="60"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="62"/>
+    </row>
+    <row r="8" spans="1:20" ht="24.2" customHeight="1">
+      <c r="A8" s="52">
+        <f>A7+1</f>
+        <v>6</v>
+      </c>
+      <c r="B8" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="60"/>
+      <c r="N8" s="61"/>
+      <c r="O8" s="61"/>
+      <c r="P8" s="62"/>
+      <c r="Q8" s="60"/>
+      <c r="R8" s="61"/>
+      <c r="S8" s="61"/>
+      <c r="T8" s="62"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="8" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;D 印刷&amp;R&amp;12( &amp;P / &amp;N )　</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2A71A9-642E-4EA6-A2C5-B57A393C2D99}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4906,19 +5790,19 @@
     </row>
     <row r="4" spans="1:103" ht="24.75" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="63">
+      <c r="B4" s="65">
         <v>1</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="67" t="s">
         <v>43</v>
       </c>
       <c r="E4" s="24">
         <v>45961</v>
       </c>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="69" t="s">
         <v>75</v>
       </c>
       <c r="G4" s="32" t="s">
@@ -5039,17 +5923,17 @@
     </row>
     <row r="5" spans="1:103" ht="24.75" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="64"/>
+      <c r="B5" s="66"/>
       <c r="C5" s="45" t="str">
         <f>C4</f>
         <v>WF開発</v>
       </c>
-      <c r="D5" s="66"/>
+      <c r="D5" s="68"/>
       <c r="E5" s="33">
         <f>IF(ISBLANK(E4),"",E4)</f>
         <v>45961</v>
       </c>
-      <c r="F5" s="68"/>
+      <c r="F5" s="70"/>
       <c r="G5" s="17" t="str">
         <f>G4</f>
         <v>榎本</v>
@@ -5164,20 +6048,20 @@
     </row>
     <row r="6" spans="1:103" ht="24.75" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="63">
+      <c r="B6" s="65">
         <f>B4+1</f>
         <v>2</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="24">
         <v>45961</v>
       </c>
-      <c r="F6" s="67" t="s">
+      <c r="F6" s="69" t="s">
         <v>75</v>
       </c>
       <c r="G6" s="32" t="s">
@@ -5296,17 +6180,17 @@
     </row>
     <row r="7" spans="1:103" ht="20.25" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="64"/>
+      <c r="B7" s="66"/>
       <c r="C7" s="45" t="str">
         <f>C6</f>
         <v>WF開発</v>
       </c>
-      <c r="D7" s="66"/>
+      <c r="D7" s="68"/>
       <c r="E7" s="33">
         <f>IF(ISBLANK(E6),"",E6)</f>
         <v>45961</v>
       </c>
-      <c r="F7" s="68"/>
+      <c r="F7" s="70"/>
       <c r="G7" s="17" t="str">
         <f>G6</f>
         <v>榎本</v>
@@ -5419,20 +6303,20 @@
     </row>
     <row r="8" spans="1:103" ht="24.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="63">
+      <c r="B8" s="65">
         <f>B6+1</f>
         <v>3</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="65" t="s">
+      <c r="D8" s="67" t="s">
         <v>46</v>
       </c>
       <c r="E8" s="24">
         <v>45961</v>
       </c>
-      <c r="F8" s="67" t="s">
+      <c r="F8" s="69" t="s">
         <v>76</v>
       </c>
       <c r="G8" s="32" t="s">
@@ -5549,17 +6433,17 @@
     </row>
     <row r="9" spans="1:103" ht="20.25" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="64"/>
+      <c r="B9" s="66"/>
       <c r="C9" s="45" t="str">
         <f>C8</f>
         <v>WF開発</v>
       </c>
-      <c r="D9" s="66"/>
+      <c r="D9" s="68"/>
       <c r="E9" s="33">
         <f>IF(ISBLANK(E8),"",E8)</f>
         <v>45961</v>
       </c>
-      <c r="F9" s="68"/>
+      <c r="F9" s="70"/>
       <c r="G9" s="17" t="str">
         <f>G8</f>
         <v>榎本</v>
@@ -5670,20 +6554,20 @@
     </row>
     <row r="10" spans="1:103" ht="24.75" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="63">
+      <c r="B10" s="65">
         <f>B6+1</f>
         <v>3</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="65" t="s">
+      <c r="D10" s="67" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="24">
         <v>45961</v>
       </c>
-      <c r="F10" s="67"/>
+      <c r="F10" s="69"/>
       <c r="G10" s="32" t="s">
         <v>22</v>
       </c>
@@ -5800,17 +6684,17 @@
     </row>
     <row r="11" spans="1:103" ht="20.25" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="64"/>
+      <c r="B11" s="66"/>
       <c r="C11" s="45" t="str">
         <f>C10</f>
         <v>WF開発</v>
       </c>
-      <c r="D11" s="66"/>
+      <c r="D11" s="68"/>
       <c r="E11" s="33">
         <f>IF(ISBLANK(E10),"",E10)</f>
         <v>45961</v>
       </c>
-      <c r="F11" s="68"/>
+      <c r="F11" s="70"/>
       <c r="G11" s="17" t="str">
         <f>G10</f>
         <v>榎本</v>
@@ -5923,20 +6807,20 @@
     </row>
     <row r="12" spans="1:103" ht="24.75" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="63">
+      <c r="B12" s="65">
         <f t="shared" ref="B12:B52" si="3">B10+1</f>
         <v>4</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="67" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="24">
         <v>45961</v>
       </c>
-      <c r="F12" s="67"/>
+      <c r="F12" s="69"/>
       <c r="G12" s="32" t="s">
         <v>22</v>
       </c>
@@ -6053,17 +6937,17 @@
     </row>
     <row r="13" spans="1:103" ht="20.25" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="64"/>
+      <c r="B13" s="66"/>
       <c r="C13" s="45" t="str">
         <f>C12</f>
         <v>WF開発</v>
       </c>
-      <c r="D13" s="66"/>
+      <c r="D13" s="68"/>
       <c r="E13" s="33">
         <f>IF(ISBLANK(E12),"",E12)</f>
         <v>45961</v>
       </c>
-      <c r="F13" s="68"/>
+      <c r="F13" s="70"/>
       <c r="G13" s="17" t="str">
         <f>G12</f>
         <v>榎本</v>
@@ -6176,20 +7060,20 @@
     </row>
     <row r="14" spans="1:103" ht="24.75" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="63">
+      <c r="B14" s="65">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="65" t="s">
+      <c r="D14" s="67" t="s">
         <v>48</v>
       </c>
       <c r="E14" s="24">
         <v>45961</v>
       </c>
-      <c r="F14" s="67"/>
+      <c r="F14" s="69"/>
       <c r="G14" s="32" t="s">
         <v>22</v>
       </c>
@@ -6306,17 +7190,17 @@
     </row>
     <row r="15" spans="1:103" ht="20.25" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="64"/>
+      <c r="B15" s="66"/>
       <c r="C15" s="45" t="str">
         <f>C14</f>
         <v>WF開発</v>
       </c>
-      <c r="D15" s="66"/>
+      <c r="D15" s="68"/>
       <c r="E15" s="33">
         <f>IF(ISBLANK(E14),"",E14)</f>
         <v>45961</v>
       </c>
-      <c r="F15" s="68"/>
+      <c r="F15" s="70"/>
       <c r="G15" s="17" t="str">
         <f>G14</f>
         <v>榎本</v>
@@ -6431,20 +7315,20 @@
     </row>
     <row r="16" spans="1:103" ht="24.75" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="63">
+      <c r="B16" s="65">
         <f>B14+1</f>
         <v>6</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="67" t="s">
         <v>49</v>
       </c>
       <c r="E16" s="24">
         <v>45961</v>
       </c>
-      <c r="F16" s="67" t="s">
+      <c r="F16" s="69" t="s">
         <v>50</v>
       </c>
       <c r="G16" s="32" t="s">
@@ -6565,17 +7449,17 @@
     </row>
     <row r="17" spans="1:103" ht="20.25" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="64"/>
+      <c r="B17" s="66"/>
       <c r="C17" s="45" t="str">
         <f>C16</f>
         <v>WF設定</v>
       </c>
-      <c r="D17" s="66"/>
+      <c r="D17" s="68"/>
       <c r="E17" s="33">
         <f>IF(ISBLANK(E16),"",E16)</f>
         <v>45961</v>
       </c>
-      <c r="F17" s="68"/>
+      <c r="F17" s="70"/>
       <c r="G17" s="17" t="str">
         <f>G16</f>
         <v>榎本</v>
@@ -6688,20 +7572,20 @@
     </row>
     <row r="18" spans="1:103" ht="24.75" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="63">
+      <c r="B18" s="65">
         <f>B14+1</f>
         <v>6</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="65" t="s">
+      <c r="D18" s="67" t="s">
         <v>51</v>
       </c>
       <c r="E18" s="24">
         <v>45961</v>
       </c>
-      <c r="F18" s="67" t="s">
+      <c r="F18" s="69" t="s">
         <v>52</v>
       </c>
       <c r="G18" s="32" t="s">
@@ -6816,17 +7700,17 @@
     </row>
     <row r="19" spans="1:103" ht="20.25" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="64"/>
+      <c r="B19" s="66"/>
       <c r="C19" s="45" t="str">
         <f>C18</f>
         <v>WF設定</v>
       </c>
-      <c r="D19" s="66"/>
+      <c r="D19" s="68"/>
       <c r="E19" s="33">
         <f>IF(ISBLANK(E18),"",E18)</f>
         <v>45961</v>
       </c>
-      <c r="F19" s="68"/>
+      <c r="F19" s="70"/>
       <c r="G19" s="17" t="str">
         <f>G18</f>
         <v>榎本</v>
@@ -6935,20 +7819,20 @@
     </row>
     <row r="20" spans="1:103" ht="24.75" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="63">
+      <c r="B20" s="65">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D20" s="67" t="s">
         <v>53</v>
       </c>
       <c r="E20" s="24">
         <v>45961</v>
       </c>
-      <c r="F20" s="67"/>
+      <c r="F20" s="69"/>
       <c r="G20" s="32" t="s">
         <v>22</v>
       </c>
@@ -7061,17 +7945,17 @@
     </row>
     <row r="21" spans="1:103" ht="20.25" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="64"/>
+      <c r="B21" s="66"/>
       <c r="C21" s="45" t="str">
         <f>C20</f>
         <v>EAI連携</v>
       </c>
-      <c r="D21" s="66"/>
+      <c r="D21" s="68"/>
       <c r="E21" s="33">
         <f>IF(ISBLANK(E20),"",E20)</f>
         <v>45961</v>
       </c>
-      <c r="F21" s="68"/>
+      <c r="F21" s="70"/>
       <c r="G21" s="17" t="str">
         <f>G20</f>
         <v>榎本</v>
@@ -7180,20 +8064,20 @@
     </row>
     <row r="22" spans="1:103" ht="24.75" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="63">
+      <c r="B22" s="65">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="65" t="s">
+      <c r="D22" s="67" t="s">
         <v>54</v>
       </c>
       <c r="E22" s="24">
         <v>45961</v>
       </c>
-      <c r="F22" s="67"/>
+      <c r="F22" s="69"/>
       <c r="G22" s="32" t="s">
         <v>22</v>
       </c>
@@ -7306,17 +8190,17 @@
     </row>
     <row r="23" spans="1:103" ht="20.25" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="64"/>
+      <c r="B23" s="66"/>
       <c r="C23" s="45" t="str">
         <f>C22</f>
         <v>EAI連携</v>
       </c>
-      <c r="D23" s="66"/>
+      <c r="D23" s="68"/>
       <c r="E23" s="33">
         <f>IF(ISBLANK(E22),"",E22)</f>
         <v>45961</v>
       </c>
-      <c r="F23" s="68"/>
+      <c r="F23" s="70"/>
       <c r="G23" s="17" t="str">
         <f>G22</f>
         <v>榎本</v>
@@ -7425,20 +8309,20 @@
     </row>
     <row r="24" spans="1:103" ht="24.75" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="63">
+      <c r="B24" s="65">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="65" t="s">
+      <c r="D24" s="67" t="s">
         <v>55</v>
       </c>
       <c r="E24" s="24">
         <v>45961</v>
       </c>
-      <c r="F24" s="67"/>
+      <c r="F24" s="69"/>
       <c r="G24" s="32" t="s">
         <v>22</v>
       </c>
@@ -7551,17 +8435,17 @@
     </row>
     <row r="25" spans="1:103" ht="20.25" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="64"/>
+      <c r="B25" s="66"/>
       <c r="C25" s="45" t="str">
         <f>C24</f>
         <v>EAI連携</v>
       </c>
-      <c r="D25" s="66"/>
+      <c r="D25" s="68"/>
       <c r="E25" s="33">
         <f>IF(ISBLANK(E24),"",E24)</f>
         <v>45961</v>
       </c>
-      <c r="F25" s="68"/>
+      <c r="F25" s="70"/>
       <c r="G25" s="17" t="str">
         <f>G24</f>
         <v>榎本</v>
@@ -7670,20 +8554,20 @@
     </row>
     <row r="26" spans="1:103" ht="24.75" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="63">
+      <c r="B26" s="65">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="65" t="s">
+      <c r="D26" s="67" t="s">
         <v>56</v>
       </c>
       <c r="E26" s="24">
         <v>45961</v>
       </c>
-      <c r="F26" s="67" t="s">
+      <c r="F26" s="69" t="s">
         <v>57</v>
       </c>
       <c r="G26" s="32" t="s">
@@ -7798,17 +8682,17 @@
     </row>
     <row r="27" spans="1:103" ht="20.25" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="64"/>
+      <c r="B27" s="66"/>
       <c r="C27" s="45" t="str">
         <f>C26</f>
         <v>WF設定</v>
       </c>
-      <c r="D27" s="66"/>
+      <c r="D27" s="68"/>
       <c r="E27" s="33">
         <f>IF(ISBLANK(E26),"",E26)</f>
         <v>45961</v>
       </c>
-      <c r="F27" s="68"/>
+      <c r="F27" s="70"/>
       <c r="G27" s="17" t="str">
         <f>G26</f>
         <v>榎本</v>
@@ -7917,20 +8801,20 @@
     </row>
     <row r="28" spans="1:103" ht="24.75" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="63">
+      <c r="B28" s="65">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="67" t="s">
         <v>58</v>
       </c>
       <c r="E28" s="24">
         <v>45961</v>
       </c>
-      <c r="F28" s="67" t="s">
+      <c r="F28" s="69" t="s">
         <v>62</v>
       </c>
       <c r="G28" s="32" t="s">
@@ -8045,17 +8929,17 @@
     </row>
     <row r="29" spans="1:103" ht="20.25" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="64"/>
+      <c r="B29" s="66"/>
       <c r="C29" s="45" t="str">
         <f>C28</f>
         <v>WF設定</v>
       </c>
-      <c r="D29" s="66"/>
+      <c r="D29" s="68"/>
       <c r="E29" s="33">
         <f>IF(ISBLANK(E28),"",E28)</f>
         <v>45961</v>
       </c>
-      <c r="F29" s="68"/>
+      <c r="F29" s="70"/>
       <c r="G29" s="17" t="str">
         <f>G28</f>
         <v>榎本</v>
@@ -8164,20 +9048,20 @@
     </row>
     <row r="30" spans="1:103" ht="24.75" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="63">
+      <c r="B30" s="65">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="65" t="s">
+      <c r="D30" s="67" t="s">
         <v>59</v>
       </c>
       <c r="E30" s="24">
         <v>45961</v>
       </c>
-      <c r="F30" s="67" t="s">
+      <c r="F30" s="69" t="s">
         <v>63</v>
       </c>
       <c r="G30" s="32" t="s">
@@ -8292,17 +9176,17 @@
     </row>
     <row r="31" spans="1:103" ht="20.25" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="64"/>
+      <c r="B31" s="66"/>
       <c r="C31" s="45" t="str">
         <f>C30</f>
         <v>WF設定</v>
       </c>
-      <c r="D31" s="66"/>
+      <c r="D31" s="68"/>
       <c r="E31" s="33">
         <f>IF(ISBLANK(E30),"",E30)</f>
         <v>45961</v>
       </c>
-      <c r="F31" s="68"/>
+      <c r="F31" s="70"/>
       <c r="G31" s="17" t="str">
         <f>G30</f>
         <v>榎本</v>
@@ -8411,20 +9295,20 @@
     </row>
     <row r="32" spans="1:103" ht="24.75" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="63">
+      <c r="B32" s="65">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="65" t="s">
+      <c r="D32" s="67" t="s">
         <v>60</v>
       </c>
       <c r="E32" s="24">
         <v>45961</v>
       </c>
-      <c r="F32" s="67" t="s">
+      <c r="F32" s="69" t="s">
         <v>64</v>
       </c>
       <c r="G32" s="32" t="s">
@@ -8539,17 +9423,17 @@
     </row>
     <row r="33" spans="1:103" ht="20.25" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="64"/>
+      <c r="B33" s="66"/>
       <c r="C33" s="45" t="str">
         <f>C32</f>
         <v>WF設定</v>
       </c>
-      <c r="D33" s="66"/>
+      <c r="D33" s="68"/>
       <c r="E33" s="33">
         <f>IF(ISBLANK(E32),"",E32)</f>
         <v>45961</v>
       </c>
-      <c r="F33" s="68"/>
+      <c r="F33" s="70"/>
       <c r="G33" s="17" t="str">
         <f>G32</f>
         <v>榎本</v>
@@ -8658,20 +9542,20 @@
     </row>
     <row r="34" spans="1:103" ht="24.75" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="63">
+      <c r="B34" s="65">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="65" t="s">
+      <c r="D34" s="67" t="s">
         <v>61</v>
       </c>
       <c r="E34" s="24">
         <v>45961</v>
       </c>
-      <c r="F34" s="67"/>
+      <c r="F34" s="69"/>
       <c r="G34" s="32" t="s">
         <v>22</v>
       </c>
@@ -8784,17 +9668,17 @@
     </row>
     <row r="35" spans="1:103" ht="20.25" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="64"/>
+      <c r="B35" s="66"/>
       <c r="C35" s="45" t="str">
         <f>C34</f>
         <v>手順書</v>
       </c>
-      <c r="D35" s="66"/>
+      <c r="D35" s="68"/>
       <c r="E35" s="33">
         <f>IF(ISBLANK(E34),"",E34)</f>
         <v>45961</v>
       </c>
-      <c r="F35" s="68"/>
+      <c r="F35" s="70"/>
       <c r="G35" s="17" t="str">
         <f>G34</f>
         <v>榎本</v>
@@ -8903,20 +9787,20 @@
     </row>
     <row r="36" spans="1:103" ht="24.75" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="63">
+      <c r="B36" s="65">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="65" t="s">
+      <c r="D36" s="67" t="s">
         <v>66</v>
       </c>
       <c r="E36" s="24">
         <v>45961</v>
       </c>
-      <c r="F36" s="67"/>
+      <c r="F36" s="69"/>
       <c r="G36" s="32" t="s">
         <v>22</v>
       </c>
@@ -9029,17 +9913,17 @@
     </row>
     <row r="37" spans="1:103" ht="20.25" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="64"/>
+      <c r="B37" s="66"/>
       <c r="C37" s="45" t="str">
         <f>C36</f>
         <v>手順書</v>
       </c>
-      <c r="D37" s="66"/>
+      <c r="D37" s="68"/>
       <c r="E37" s="33">
         <f>IF(ISBLANK(E36),"",E36)</f>
         <v>45961</v>
       </c>
-      <c r="F37" s="68"/>
+      <c r="F37" s="70"/>
       <c r="G37" s="17" t="str">
         <f>G36</f>
         <v>榎本</v>
@@ -9148,20 +10032,20 @@
     </row>
     <row r="38" spans="1:103" ht="24.75" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="63">
+      <c r="B38" s="65">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="65" t="s">
+      <c r="D38" s="67" t="s">
         <v>67</v>
       </c>
       <c r="E38" s="24">
         <v>45961</v>
       </c>
-      <c r="F38" s="67"/>
+      <c r="F38" s="69"/>
       <c r="G38" s="32" t="s">
         <v>22</v>
       </c>
@@ -9274,17 +10158,17 @@
     </row>
     <row r="39" spans="1:103" ht="20.25" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="64"/>
+      <c r="B39" s="66"/>
       <c r="C39" s="45" t="str">
         <f>C38</f>
         <v>手順書</v>
       </c>
-      <c r="D39" s="66"/>
+      <c r="D39" s="68"/>
       <c r="E39" s="33">
         <f>IF(ISBLANK(E38),"",E38)</f>
         <v>45961</v>
       </c>
-      <c r="F39" s="68"/>
+      <c r="F39" s="70"/>
       <c r="G39" s="17" t="str">
         <f>G38</f>
         <v>榎本</v>
@@ -9393,20 +10277,20 @@
     </row>
     <row r="40" spans="1:103" ht="24.75" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="63">
+      <c r="B40" s="65">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="65" t="s">
+      <c r="D40" s="67" t="s">
         <v>68</v>
       </c>
       <c r="E40" s="24">
         <v>45961</v>
       </c>
-      <c r="F40" s="67"/>
+      <c r="F40" s="69"/>
       <c r="G40" s="32" t="s">
         <v>22</v>
       </c>
@@ -9519,17 +10403,17 @@
     </row>
     <row r="41" spans="1:103" ht="20.25" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="64"/>
+      <c r="B41" s="66"/>
       <c r="C41" s="45" t="str">
         <f>C40</f>
         <v>手順書</v>
       </c>
-      <c r="D41" s="66"/>
+      <c r="D41" s="68"/>
       <c r="E41" s="33">
         <f>IF(ISBLANK(E40),"",E40)</f>
         <v>45961</v>
       </c>
-      <c r="F41" s="68"/>
+      <c r="F41" s="70"/>
       <c r="G41" s="17" t="str">
         <f>G40</f>
         <v>榎本</v>
@@ -9638,20 +10522,20 @@
     </row>
     <row r="42" spans="1:103" ht="24.75" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="63">
+      <c r="B42" s="65">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="65" t="s">
+      <c r="D42" s="67" t="s">
         <v>69</v>
       </c>
       <c r="E42" s="24">
         <v>45961</v>
       </c>
-      <c r="F42" s="67"/>
+      <c r="F42" s="69"/>
       <c r="G42" s="32" t="s">
         <v>22</v>
       </c>
@@ -9764,17 +10648,17 @@
     </row>
     <row r="43" spans="1:103" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="64"/>
+      <c r="B43" s="66"/>
       <c r="C43" s="45" t="str">
         <f>C42</f>
         <v>手順書</v>
       </c>
-      <c r="D43" s="66"/>
+      <c r="D43" s="68"/>
       <c r="E43" s="33">
         <f>IF(ISBLANK(E42),"",E42)</f>
         <v>45961</v>
       </c>
-      <c r="F43" s="68"/>
+      <c r="F43" s="70"/>
       <c r="G43" s="17" t="str">
         <f>G42</f>
         <v>榎本</v>
@@ -9883,20 +10767,20 @@
     </row>
     <row r="44" spans="1:103" ht="24.75" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="63">
+      <c r="B44" s="65">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D44" s="65" t="s">
+      <c r="D44" s="67" t="s">
         <v>70</v>
       </c>
       <c r="E44" s="24">
         <v>45884</v>
       </c>
-      <c r="F44" s="67"/>
+      <c r="F44" s="69"/>
       <c r="G44" s="32" t="s">
         <v>22</v>
       </c>
@@ -10009,17 +10893,17 @@
     </row>
     <row r="45" spans="1:103" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="64"/>
+      <c r="B45" s="66"/>
       <c r="C45" s="45" t="str">
         <f>C44</f>
         <v>環境構築</v>
       </c>
-      <c r="D45" s="66"/>
+      <c r="D45" s="68"/>
       <c r="E45" s="33">
         <f>IF(ISBLANK(E44),"",E44)</f>
         <v>45884</v>
       </c>
-      <c r="F45" s="68"/>
+      <c r="F45" s="70"/>
       <c r="G45" s="17" t="str">
         <f>G44</f>
         <v>榎本</v>
@@ -10128,20 +11012,20 @@
     </row>
     <row r="46" spans="1:103" ht="24.75" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="63">
+      <c r="B46" s="65">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D46" s="65" t="s">
+      <c r="D46" s="67" t="s">
         <v>71</v>
       </c>
       <c r="E46" s="24">
         <v>45975</v>
       </c>
-      <c r="F46" s="67"/>
+      <c r="F46" s="69"/>
       <c r="G46" s="32" t="s">
         <v>22</v>
       </c>
@@ -10254,17 +11138,17 @@
     </row>
     <row r="47" spans="1:103" ht="20.25" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="64"/>
+      <c r="B47" s="66"/>
       <c r="C47" s="45" t="str">
         <f>C46</f>
         <v>環境構築</v>
       </c>
-      <c r="D47" s="66"/>
+      <c r="D47" s="68"/>
       <c r="E47" s="33">
         <f>IF(ISBLANK(E46),"",E46)</f>
         <v>45975</v>
       </c>
-      <c r="F47" s="68"/>
+      <c r="F47" s="70"/>
       <c r="G47" s="17" t="str">
         <f>G46</f>
         <v>榎本</v>
@@ -10373,20 +11257,20 @@
     </row>
     <row r="48" spans="1:103" ht="24.75" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="63">
+      <c r="B48" s="65">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="65" t="s">
+      <c r="D48" s="67" t="s">
         <v>72</v>
       </c>
       <c r="E48" s="24">
         <v>46003</v>
       </c>
-      <c r="F48" s="67"/>
+      <c r="F48" s="69"/>
       <c r="G48" s="32" t="s">
         <v>22</v>
       </c>
@@ -10499,17 +11383,17 @@
     </row>
     <row r="49" spans="1:103" ht="20.25" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="64"/>
+      <c r="B49" s="66"/>
       <c r="C49" s="45" t="str">
         <f>C48</f>
         <v>環境構築</v>
       </c>
-      <c r="D49" s="66"/>
+      <c r="D49" s="68"/>
       <c r="E49" s="33">
         <f>IF(ISBLANK(E48),"",E48)</f>
         <v>46003</v>
       </c>
-      <c r="F49" s="68"/>
+      <c r="F49" s="70"/>
       <c r="G49" s="17" t="str">
         <f>G48</f>
         <v>榎本</v>
@@ -10618,20 +11502,20 @@
     </row>
     <row r="50" spans="1:103" ht="24.75" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="63">
+      <c r="B50" s="65">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D50" s="65" t="s">
+      <c r="D50" s="67" t="s">
         <v>73</v>
       </c>
       <c r="E50" s="24">
         <v>46003</v>
       </c>
-      <c r="F50" s="67"/>
+      <c r="F50" s="69"/>
       <c r="G50" s="32" t="s">
         <v>22</v>
       </c>
@@ -10744,17 +11628,17 @@
     </row>
     <row r="51" spans="1:103" ht="20.25" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="64"/>
+      <c r="B51" s="66"/>
       <c r="C51" s="45" t="str">
         <f>C50</f>
         <v>性能試験</v>
       </c>
-      <c r="D51" s="66"/>
+      <c r="D51" s="68"/>
       <c r="E51" s="33">
         <f>IF(ISBLANK(E50),"",E50)</f>
         <v>46003</v>
       </c>
-      <c r="F51" s="68"/>
+      <c r="F51" s="70"/>
       <c r="G51" s="17" t="str">
         <f>G50</f>
         <v>榎本</v>
@@ -10863,20 +11747,20 @@
     </row>
     <row r="52" spans="1:103" ht="24.75" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="63">
+      <c r="B52" s="65">
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D52" s="65" t="s">
+      <c r="D52" s="67" t="s">
         <v>74</v>
       </c>
       <c r="E52" s="24">
         <v>46022</v>
       </c>
-      <c r="F52" s="67"/>
+      <c r="F52" s="69"/>
       <c r="G52" s="32" t="s">
         <v>22</v>
       </c>
@@ -10989,17 +11873,17 @@
     </row>
     <row r="53" spans="1:103" ht="20.25" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="64"/>
+      <c r="B53" s="66"/>
       <c r="C53" s="45" t="str">
         <f>C52</f>
         <v>性能試験</v>
       </c>
-      <c r="D53" s="66"/>
+      <c r="D53" s="68"/>
       <c r="E53" s="33">
         <f>IF(ISBLANK(E52),"",E52)</f>
         <v>46022</v>
       </c>
-      <c r="F53" s="68"/>
+      <c r="F53" s="70"/>
       <c r="G53" s="17" t="str">
         <f>G52</f>
         <v>榎本</v>
@@ -11109,6 +11993,72 @@
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="75">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="F46:F47"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="F52:F53"/>
@@ -11118,72 +12068,6 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="F50:F51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E4">
@@ -11312,14 +12196,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L53">
-    <cfRule type="cellIs" dxfId="26" priority="52" stopIfTrue="1" operator="equal">
-      <formula>"完了"</formula>
-    </cfRule>
-    <cfRule type="timePeriod" dxfId="25" priority="50" timePeriod="nextWeek">
+    <cfRule type="timePeriod" dxfId="26" priority="50" timePeriod="nextWeek">
       <formula>AND(ROUNDDOWN(L4,0)-TODAY()&gt;(7-WEEKDAY(TODAY())),ROUNDDOWN(L4,0)-TODAY()&lt;(15-WEEKDAY(TODAY())))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="24" priority="51" timePeriod="thisWeek">
+    <cfRule type="timePeriod" dxfId="25" priority="51" timePeriod="thisWeek">
       <formula>AND(TODAY()-ROUNDDOWN(L4,0)&lt;=WEEKDAY(TODAY())-1,ROUNDDOWN(L4,0)-TODAY()&lt;=7-WEEKDAY(TODAY()))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="52" stopIfTrue="1" operator="equal">
+      <formula>"完了"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
@@ -11459,7 +12343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D16"/>

--- a/90_管理/作業スケジュール.xlsx
+++ b/90_管理/作業スケジュール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301043D1-7820-410B-9A3B-F8AC24E6034E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EF7194-995C-4018-99FC-52C98119DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="75" windowWidth="22680" windowHeight="13305" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4050" yWindow="1755" windowWidth="24750" windowHeight="13065" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="17" r:id="rId1"/>
@@ -2705,18 +2705,6 @@
       <font>
         <b/>
         <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
       <fill>
@@ -2732,6 +2720,18 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3779,14 +3779,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>179296</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>145678</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>179296</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>145678</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3803,7 +3803,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8001002" y="493059"/>
+          <a:off x="4953002" y="493059"/>
           <a:ext cx="0" cy="1848970"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -11993,72 +11993,6 @@
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="75">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="F46:F47"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="F52:F53"/>
@@ -12068,6 +12002,72 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="F50:F51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E4">
@@ -12196,14 +12196,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L53">
-    <cfRule type="timePeriod" dxfId="26" priority="50" timePeriod="nextWeek">
+    <cfRule type="cellIs" dxfId="26" priority="52" stopIfTrue="1" operator="equal">
+      <formula>"完了"</formula>
+    </cfRule>
+    <cfRule type="timePeriod" dxfId="25" priority="50" timePeriod="nextWeek">
       <formula>AND(ROUNDDOWN(L4,0)-TODAY()&gt;(7-WEEKDAY(TODAY())),ROUNDDOWN(L4,0)-TODAY()&lt;(15-WEEKDAY(TODAY())))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="25" priority="51" timePeriod="thisWeek">
+    <cfRule type="timePeriod" dxfId="24" priority="51" timePeriod="thisWeek">
       <formula>AND(TODAY()-ROUNDDOWN(L4,0)&lt;=WEEKDAY(TODAY())-1,ROUNDDOWN(L4,0)-TODAY()&lt;=7-WEEKDAY(TODAY()))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="52" stopIfTrue="1" operator="equal">
-      <formula>"完了"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">

--- a/90_管理/作業スケジュール.xlsx
+++ b/90_管理/作業スケジュール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EF7194-995C-4018-99FC-52C98119DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17D8C9B-13B5-4BB2-9392-7B2B5179E29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4050" yWindow="1755" windowWidth="24750" windowHeight="13065" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3225" yWindow="1365" windowWidth="24060" windowHeight="13035" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="17" r:id="rId1"/>
@@ -3779,14 +3779,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>145678</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>156884</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>145678</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>156884</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3803,7 +3803,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4953002" y="493059"/>
+          <a:off x="5311590" y="493059"/>
           <a:ext cx="0" cy="1848970"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -11993,6 +11993,72 @@
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="75">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="F46:F47"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="F52:F53"/>
@@ -12002,72 +12068,6 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="F50:F51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E4">

--- a/90_管理/作業スケジュール.xlsx
+++ b/90_管理/作業スケジュール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17D8C9B-13B5-4BB2-9392-7B2B5179E29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD84D1C-27BF-4086-861E-BEA29340CD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3225" yWindow="1365" windowWidth="24060" windowHeight="13035" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="345" windowWidth="23520" windowHeight="13065" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="17" r:id="rId1"/>
@@ -3779,14 +3779,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>156884</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>168091</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>156884</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>168091</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3803,7 +3803,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5311590" y="493059"/>
+          <a:off x="5670179" y="493059"/>
           <a:ext cx="0" cy="1848970"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -11993,72 +11993,6 @@
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="75">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="F46:F47"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="F52:F53"/>
@@ -12068,6 +12002,72 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="F50:F51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E4">

--- a/90_管理/作業スケジュール.xlsx
+++ b/90_管理/作業スケジュール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD84D1C-27BF-4086-861E-BEA29340CD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3618E6-A07B-4170-A193-38BE830BFE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="345" windowWidth="23520" windowHeight="13065" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="930" yWindow="1635" windowWidth="27585" windowHeight="13065" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="17" r:id="rId1"/>
@@ -3779,14 +3779,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>168091</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>179296</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>168091</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>179296</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3803,7 +3803,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5670179" y="493059"/>
+          <a:off x="6028767" y="493059"/>
           <a:ext cx="0" cy="1848970"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -11993,6 +11993,72 @@
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="75">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="F46:F47"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="F52:F53"/>
@@ -12002,72 +12068,6 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="F50:F51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E4">

--- a/90_管理/作業スケジュール.xlsx
+++ b/90_管理/作業スケジュール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3618E6-A07B-4170-A193-38BE830BFE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BFF436-4182-4A41-8187-4ACF9CAC0094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="1635" windowWidth="27585" windowHeight="13065" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7185" yWindow="0" windowWidth="15570" windowHeight="15585" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="17" r:id="rId1"/>
@@ -11993,72 +11993,6 @@
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="75">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="F46:F47"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="F52:F53"/>
@@ -12068,6 +12002,72 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="F50:F51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E4">

--- a/90_管理/作業スケジュール.xlsx
+++ b/90_管理/作業スケジュール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BFF436-4182-4A41-8187-4ACF9CAC0094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064A80E1-4C95-4C12-8BDE-E10E487B11D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7185" yWindow="0" windowWidth="15570" windowHeight="15585" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5145" yWindow="1740" windowWidth="23460" windowHeight="12645" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="17" r:id="rId1"/>
@@ -3779,14 +3779,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>179296</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>156884</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>179296</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>156884</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3803,7 +3803,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6028767" y="493059"/>
+          <a:off x="6353737" y="493059"/>
           <a:ext cx="0" cy="1848970"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -11993,6 +11993,72 @@
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="75">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="F46:F47"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="F52:F53"/>
@@ -12002,72 +12068,6 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="F50:F51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E4">

--- a/90_管理/作業スケジュール.xlsx
+++ b/90_管理/作業スケジュール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064A80E1-4C95-4C12-8BDE-E10E487B11D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99DF3DA-0909-4360-B562-C506FA550CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5145" yWindow="1740" windowWidth="23460" windowHeight="12645" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4830" yWindow="255" windowWidth="22440" windowHeight="14475" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="17" r:id="rId1"/>
@@ -3779,14 +3779,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>156884</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>190502</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>156884</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>190502</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3803,7 +3803,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6353737" y="493059"/>
+          <a:off x="6734737" y="493059"/>
           <a:ext cx="0" cy="1848970"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -11993,72 +11993,6 @@
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="75">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="F46:F47"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="F52:F53"/>
@@ -12068,6 +12002,72 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="F50:F51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E4">

--- a/90_管理/作業スケジュール.xlsx
+++ b/90_管理/作業スケジュール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\90_管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99DF3DA-0909-4360-B562-C506FA550CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6598E8EB-2217-4B76-B2DB-B96615B4CE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4830" yWindow="255" windowWidth="22440" windowHeight="14475" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9885" yWindow="0" windowWidth="18390" windowHeight="14865" tabRatio="760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="17" r:id="rId1"/>
@@ -3526,7 +3526,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6"/>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="12700">
           <a:solidFill>
@@ -3597,7 +3599,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6"/>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="12700">
           <a:solidFill>
@@ -3668,7 +3672,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6"/>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="12700">
           <a:solidFill>
@@ -3739,7 +3745,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6"/>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="12700">
           <a:solidFill>
@@ -3779,16 +3787,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>190502</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>156884</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>347382</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>190502</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>156884</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>291352</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3803,7 +3811,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6734737" y="493059"/>
+          <a:off x="7048502" y="481853"/>
           <a:ext cx="0" cy="1848970"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -3865,7 +3873,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6"/>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="12700">
           <a:solidFill>
@@ -3936,7 +3946,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6"/>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="12700">
           <a:solidFill>
@@ -11993,6 +12005,72 @@
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="75">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="F46:F47"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="F52:F53"/>
@@ -12002,72 +12080,6 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="F50:F51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E4">
